--- a/research/traditional_assets/database/data/argentina/argentina_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_cable_tv.xlsx
@@ -588,109 +588,112 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.4124291772084239</v>
+        <v>0.506441454337246</v>
       </c>
       <c r="H2">
-        <v>0.4124291772084239</v>
+        <v>0.506441454337246</v>
       </c>
       <c r="I2">
-        <v>-0.0184228343370274</v>
+        <v>-0.06801357817676169</v>
       </c>
       <c r="J2">
-        <v>-0.009211417168513701</v>
+        <v>-0.06801357817676169</v>
       </c>
       <c r="K2">
-        <v>-17.6</v>
+        <v>-531</v>
       </c>
       <c r="L2">
-        <v>-0.00627160317856252</v>
+        <v>-0.2171690319414339</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.002397666150059258</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.004952919020715631</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.002397666150059258</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.004952919020715631</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>183.2</v>
+        <v>233.5</v>
       </c>
       <c r="V2">
-        <v>0.1735505873436908</v>
+        <v>0.2128726410794056</v>
       </c>
       <c r="W2">
-        <v>-0.008863373117792214</v>
+        <v>-0.2638509316770186</v>
       </c>
       <c r="X2">
-        <v>0.3459440784822446</v>
+        <v>0.4783543734584202</v>
       </c>
       <c r="Y2">
-        <v>-0.3548074516000368</v>
+        <v>-0.7422053051354388</v>
       </c>
       <c r="Z2">
-        <v>2.216666666666667</v>
+        <v>2.006647517439474</v>
       </c>
       <c r="AA2">
-        <v>-0.02041864139020537</v>
+        <v>-0.1364792778005744</v>
       </c>
       <c r="AB2">
-        <v>0.1674583642098061</v>
+        <v>0.2269979052031962</v>
       </c>
       <c r="AC2">
-        <v>-0.1878770056000115</v>
+        <v>-0.3634771830037706</v>
       </c>
       <c r="AD2">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AG2">
-        <v>2511.6</v>
+        <v>2644.2</v>
       </c>
       <c r="AH2">
-        <v>0.7185366894197952</v>
+        <v>0.7240225431489961</v>
       </c>
       <c r="AI2">
-        <v>0.3588999134314444</v>
+        <v>0.375482776617954</v>
       </c>
       <c r="AJ2">
-        <v>0.7040816326530612</v>
+        <v>0.70679746598594</v>
       </c>
       <c r="AK2">
-        <v>0.3428665037609381</v>
+        <v>0.355857613888702</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-160</v>
+        <v>-9.5</v>
       </c>
       <c r="AN2">
-        <v>3.427626558127703</v>
+        <v>4.965832614322692</v>
       </c>
       <c r="AP2">
-        <v>3.194606970236581</v>
+        <v>4.562899050905953</v>
       </c>
       <c r="AQ2">
-        <v>0.323125</v>
+        <v>17.50526315789474</v>
       </c>
     </row>
     <row r="3">
@@ -710,109 +713,112 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.4124291772084239</v>
+        <v>0.506441454337246</v>
       </c>
       <c r="H3">
-        <v>0.4124291772084239</v>
+        <v>0.506441454337246</v>
       </c>
       <c r="I3">
-        <v>-0.0184228343370274</v>
+        <v>-0.06801357817676169</v>
       </c>
       <c r="J3">
-        <v>-0.009211417168513701</v>
+        <v>-0.06801357817676169</v>
       </c>
       <c r="K3">
-        <v>-17.6</v>
+        <v>-531</v>
       </c>
       <c r="L3">
-        <v>-0.00627160317856252</v>
+        <v>-0.2171690319414339</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.63</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.002397666150059258</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.004952919020715631</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.63</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.002397666150059258</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0.004952919020715631</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>183.2</v>
+        <v>233.5</v>
       </c>
       <c r="V3">
-        <v>0.1735505873436908</v>
+        <v>0.2128726410794056</v>
       </c>
       <c r="W3">
-        <v>-0.008863373117792214</v>
+        <v>-0.2638509316770186</v>
       </c>
       <c r="X3">
-        <v>0.3459440784822446</v>
+        <v>0.4783543734584202</v>
       </c>
       <c r="Y3">
-        <v>-0.3548074516000368</v>
+        <v>-0.7422053051354388</v>
       </c>
       <c r="Z3">
-        <v>2.216666666666667</v>
+        <v>2.006647517439474</v>
       </c>
       <c r="AA3">
-        <v>-0.02041864139020537</v>
+        <v>-0.1364792778005744</v>
       </c>
       <c r="AB3">
-        <v>0.1674583642098061</v>
+        <v>0.2269979052031962</v>
       </c>
       <c r="AC3">
-        <v>-0.1878770056000115</v>
+        <v>-0.3634771830037706</v>
       </c>
       <c r="AD3">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AG3">
-        <v>2511.6</v>
+        <v>2644.2</v>
       </c>
       <c r="AH3">
-        <v>0.7185366894197952</v>
+        <v>0.7240225431489961</v>
       </c>
       <c r="AI3">
-        <v>0.3588999134314444</v>
+        <v>0.375482776617954</v>
       </c>
       <c r="AJ3">
-        <v>0.7040816326530612</v>
+        <v>0.70679746598594</v>
       </c>
       <c r="AK3">
-        <v>0.3428665037609381</v>
+        <v>0.355857613888702</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-160</v>
+        <v>-9.5</v>
       </c>
       <c r="AN3">
-        <v>3.427626558127703</v>
+        <v>4.965832614322692</v>
       </c>
       <c r="AP3">
-        <v>3.194606970236581</v>
+        <v>4.562899050905953</v>
       </c>
       <c r="AQ3">
-        <v>0.323125</v>
+        <v>17.50526315789474</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_cable_tv.xlsx
@@ -587,113 +587,116 @@
           <t>Cable TV</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.229</v>
+      </c>
       <c r="G2">
-        <v>0.506441454337246</v>
+        <v>0.5742590559824369</v>
       </c>
       <c r="H2">
-        <v>0.506441454337246</v>
+        <v>0.5742590559824369</v>
       </c>
       <c r="I2">
-        <v>-0.06801357817676169</v>
+        <v>-0.05192096597145993</v>
       </c>
       <c r="J2">
-        <v>-0.06801357817676169</v>
+        <v>-0.05192096597145993</v>
       </c>
       <c r="K2">
-        <v>-531</v>
+        <v>354.3</v>
       </c>
       <c r="L2">
-        <v>-0.2171690319414339</v>
+        <v>0.194456641053787</v>
       </c>
       <c r="M2">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.002397666150059258</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.004952919020715631</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.002397666150059258</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.004952919020715631</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>233.5</v>
+        <v>289</v>
       </c>
       <c r="V2">
-        <v>0.2128726410794056</v>
+        <v>0.3578947368421053</v>
       </c>
       <c r="W2">
-        <v>-0.2638509316770186</v>
+        <v>0.1921366594360087</v>
       </c>
       <c r="X2">
-        <v>0.4783543734584202</v>
+        <v>0.4643720974261814</v>
       </c>
       <c r="Y2">
-        <v>-0.7422053051354388</v>
+        <v>-0.2722354379901727</v>
       </c>
       <c r="Z2">
-        <v>2.006647517439474</v>
+        <v>1.123166070768093</v>
       </c>
       <c r="AA2">
-        <v>-0.1364792778005744</v>
+        <v>-0.0583158673406485</v>
       </c>
       <c r="AB2">
-        <v>0.2269979052031962</v>
+        <v>0.1971243512835711</v>
       </c>
       <c r="AC2">
-        <v>-0.3634771830037706</v>
+        <v>-0.2554402186242196</v>
       </c>
       <c r="AD2">
-        <v>2877.7</v>
+        <v>2789.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2877.7</v>
+        <v>2789.7</v>
       </c>
       <c r="AG2">
-        <v>2644.2</v>
+        <v>2500.7</v>
       </c>
       <c r="AH2">
-        <v>0.7240225431489961</v>
+        <v>0.7755198487712666</v>
       </c>
       <c r="AI2">
-        <v>0.375482776617954</v>
+        <v>0.3692668140362953</v>
       </c>
       <c r="AJ2">
-        <v>0.70679746598594</v>
+        <v>0.7559095580678314</v>
       </c>
       <c r="AK2">
-        <v>0.355857613888702</v>
+        <v>0.3441788127778466</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>94.2</v>
       </c>
       <c r="AM2">
-        <v>-9.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AN2">
-        <v>4.965832614322692</v>
+        <v>6.28735632183908</v>
+      </c>
+      <c r="AO2">
+        <v>-1.004246284501062</v>
       </c>
       <c r="AP2">
-        <v>4.562899050905953</v>
+        <v>5.636015325670498</v>
       </c>
       <c r="AQ2">
-        <v>17.50526315789474</v>
+        <v>-1.251322751322751</v>
       </c>
     </row>
     <row r="3">
@@ -712,113 +715,116 @@
           <t>Cable TV</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.229</v>
+      </c>
       <c r="G3">
-        <v>0.506441454337246</v>
+        <v>0.5742590559824369</v>
       </c>
       <c r="H3">
-        <v>0.506441454337246</v>
+        <v>0.5742590559824369</v>
       </c>
       <c r="I3">
-        <v>-0.06801357817676169</v>
+        <v>-0.05192096597145993</v>
       </c>
       <c r="J3">
-        <v>-0.06801357817676169</v>
+        <v>-0.05192096597145993</v>
       </c>
       <c r="K3">
-        <v>-531</v>
+        <v>354.3</v>
       </c>
       <c r="L3">
-        <v>-0.2171690319414339</v>
+        <v>0.194456641053787</v>
       </c>
       <c r="M3">
-        <v>2.63</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.002397666150059258</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.004952919020715631</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>2.63</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.002397666150059258</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.004952919020715631</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>233.5</v>
+        <v>289</v>
       </c>
       <c r="V3">
-        <v>0.2128726410794056</v>
+        <v>0.3578947368421053</v>
       </c>
       <c r="W3">
-        <v>-0.2638509316770186</v>
+        <v>0.1921366594360087</v>
       </c>
       <c r="X3">
-        <v>0.4783543734584202</v>
+        <v>0.4643720974261814</v>
       </c>
       <c r="Y3">
-        <v>-0.7422053051354388</v>
+        <v>-0.2722354379901727</v>
       </c>
       <c r="Z3">
-        <v>2.006647517439474</v>
+        <v>1.123166070768093</v>
       </c>
       <c r="AA3">
-        <v>-0.1364792778005744</v>
+        <v>-0.0583158673406485</v>
       </c>
       <c r="AB3">
-        <v>0.2269979052031962</v>
+        <v>0.1971243512835711</v>
       </c>
       <c r="AC3">
-        <v>-0.3634771830037706</v>
+        <v>-0.2554402186242196</v>
       </c>
       <c r="AD3">
-        <v>2877.7</v>
+        <v>2789.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2877.7</v>
+        <v>2789.7</v>
       </c>
       <c r="AG3">
-        <v>2644.2</v>
+        <v>2500.7</v>
       </c>
       <c r="AH3">
-        <v>0.7240225431489961</v>
+        <v>0.7755198487712666</v>
       </c>
       <c r="AI3">
-        <v>0.375482776617954</v>
+        <v>0.3692668140362953</v>
       </c>
       <c r="AJ3">
-        <v>0.70679746598594</v>
+        <v>0.7559095580678314</v>
       </c>
       <c r="AK3">
-        <v>0.355857613888702</v>
+        <v>0.3441788127778466</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>94.2</v>
       </c>
       <c r="AM3">
-        <v>-9.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AN3">
-        <v>4.965832614322692</v>
+        <v>6.28735632183908</v>
+      </c>
+      <c r="AO3">
+        <v>-1.004246284501062</v>
       </c>
       <c r="AP3">
-        <v>4.562899050905953</v>
+        <v>5.636015325670498</v>
       </c>
       <c r="AQ3">
-        <v>17.50526315789474</v>
+        <v>-1.251322751322751</v>
       </c>
     </row>
   </sheetData>
